--- a/output/pdf_financials_xlsx/ACS.xlsx
+++ b/output/pdf_financials_xlsx/ACS.xlsx
@@ -5281,40 +5281,32 @@
       <c r="E92" s="3" t="n">
         <v>1.533603</v>
       </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" s="3" t="n">
+        <v>1.533603</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.079623</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.079623</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.791103</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>2.791103</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.255023</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.965073</v>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>2.965073</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>2.965073</v>
       </c>
     </row>
     <row r="93">
@@ -8618,7 +8610,11 @@
           <t>Share-based payment reserve (note 5 (b))</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9485,7 +9481,11 @@
           <t>Share-based payment reserve (note 5 (d))</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10117,7 +10117,11 @@
           <t>Share-based payment reserve (note 5 (d))</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -10757,7 +10761,11 @@
           <t>Share-based payment reserve (note 5 (d))</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -11883,7 +11891,11 @@
           <t>Share-based payment reserve (note 4 (d))</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -12762,7 +12774,11 @@
           <t>Share-based payment reserve (note 4 (d))</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -13850,7 +13866,11 @@
           <t>Share-based payment reserve (note 5 (d))</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ACS.xlsx
+++ b/output/pdf_financials_xlsx/ACS.xlsx
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001597</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1768,10 +1768,10 @@
         <v>0.501626</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.664655</v>
+        <v>-0.666252</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.760251</v>
+        <v>-0.760441</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-15.738845</v>
@@ -1868,10 +1868,10 @@
         <v>0.501626</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.664655</v>
+        <v>-0.666252</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.760251</v>
+        <v>-0.760441</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-15.738845</v>
@@ -2106,10 +2106,10 @@
         <v>0.221042</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000239</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.023145</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.207036</v>
@@ -2118,21 +2118,19 @@
         <v>0.004712</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001336</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J34" s="3" t="n">
+        <v>0.003452</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.267212</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2212,10 +2210,10 @@
         <v>0.221042</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000239</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.023145</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.207036</v>
@@ -2224,21 +2222,19 @@
         <v>0.004712</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001336</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J36" s="3" t="n">
+        <v>0.003452</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.267212</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2842,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000239</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.023145</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -2867,10 +2863,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.267212</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -9643,7 +9639,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -14113,7 +14109,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -26936,7 +26932,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
